--- a/stores picture/倷食廚房.xlsx
+++ b/stores picture/倷食廚房.xlsx
@@ -33,9 +33,6 @@
     <t>靖魚 (單點)</t>
   </si>
   <si>
-    <t>土魠魚 (單點)</t>
-  </si>
-  <si>
     <t>五香滷雞腿便當</t>
   </si>
   <si>
@@ -55,13 +52,54 @@
   </si>
   <si>
     <t>香煎土魠魚便當</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>虱目魚肚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>單點</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -81,6 +119,13 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -426,21 +471,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -459,76 +507,76 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="B13" s="1">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/stores picture/倷食廚房.xlsx
+++ b/stores picture/倷食廚房.xlsx
@@ -16,22 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>炸排骨 (單點)</t>
-  </si>
-  <si>
-    <t>烤排骨 (單點)</t>
-  </si>
-  <si>
-    <t>炸雞腿 (單點)</t>
-  </si>
-  <si>
-    <t>滷雞腿 (單點)</t>
-  </si>
-  <si>
-    <t>靖魚 (單點)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>五香滷雞腿便當</t>
   </si>
@@ -48,50 +33,100 @@
     <t>主廚每日特餐</t>
   </si>
   <si>
-    <t>烤靖魚便當</t>
-  </si>
-  <si>
-    <t>香煎土魠魚便當</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>虱目魚肚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>單點</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
+    <t>烤鯖魚便當</t>
+  </si>
+  <si>
+    <t>虱目魚肚便當</t>
+  </si>
+  <si>
+    <t>綜合炒時蔬 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>法式舒肥雞胸 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>法式舒肥雞胸 (沙拉餐盒)</t>
+  </si>
+  <si>
+    <t>麻辣舒肥雞胸 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>麻辣舒肥雞胸 (沙拉餐盒)</t>
+  </si>
+  <si>
+    <t>檸香雞腿排 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>檸香雞腿排 (沙拉餐盒)</t>
+  </si>
+  <si>
+    <t>香煎松阪豬 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>香煎松阪豬 (沙拉餐盒)</t>
+  </si>
+  <si>
+    <t>嫩煎牛排 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>嫩煎牛排 (沙拉餐盒)</t>
+  </si>
+  <si>
+    <t>挪威香煎鮭魚 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>挪威香煎鮭魚 (沙拉餐盒)</t>
+  </si>
+  <si>
+    <t>義式鴨胸 (飯餐盒)</t>
+  </si>
+  <si>
+    <t>義式鴨胸 (沙拉餐盒)</t>
+  </si>
+  <si>
+    <t>冷泡茶</t>
+  </si>
+  <si>
+    <t>炸排骨 (快餐單點)</t>
+  </si>
+  <si>
+    <t>烤排骨 (快餐單點)</t>
+  </si>
+  <si>
+    <t>炸雞腿 (快餐單點)</t>
+  </si>
+  <si>
+    <t>滷雞腿 (快餐單點)</t>
+  </si>
+  <si>
+    <t>鯖魚 (快餐單點)</t>
+  </si>
+  <si>
+    <t>虱目魚肚 (快餐單點)</t>
+  </si>
+  <si>
+    <t>法式舒肥雞胸 (加購主餐)</t>
+  </si>
+  <si>
+    <t>麻辣舒肥雞胸 (加購主餐)</t>
+  </si>
+  <si>
+    <t>檸香雞腿排 (加購主餐)</t>
+  </si>
+  <si>
+    <t>香煎松阪豬 (加購主餐)</t>
+  </si>
+  <si>
+    <t>嫩煎牛排 (加購主餐)</t>
+  </si>
+  <si>
+    <t>挪威香煎鮭魚 (加購主餐)</t>
+  </si>
+  <si>
+    <t>義式鴨胸 (加購主餐)</t>
+  </si>
+  <si>
+    <t>凱薩,油醋,胡麻</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -99,7 +134,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -119,13 +154,6 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -469,114 +497,320 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="1" max="1" width="31.6328125" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B2" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>130</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>145</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>155</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>155</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>165</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="27" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="29" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="30" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="33" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1">
-        <v>85</v>
+    <row r="34" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="62.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
